--- a/templates/_masters/REV-002-dynamic-pricing-calculator-BLANK.xlsx
+++ b/templates/_masters/REV-002-dynamic-pricing-calculator-BLANK.xlsx
@@ -447,14 +447,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00C8E6C9"/>
+          <fgColor rgb="00C7EFCF"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00FFD6D6"/>
+          <fgColor rgb="00FFCCCC"/>
         </patternFill>
       </fill>
     </dxf>
